--- a/Labs/Lab4_ADC/New Microsoft Excel Worksheet.xlsx
+++ b/Labs/Lab4_ADC/New Microsoft Excel Worksheet.xlsx
@@ -5,27 +5,34 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\bzha931\Documents\GitHub\Lab-209\Labs\Lab4_ADC\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://uoa-my.sharepoint.com/personal/bzha931_uoa_auckland_ac_nz/Documents/Documents/GitHub/Lab-209/Labs/Lab4_ADC/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{110ACAF4-5F87-42D2-BA49-A95FA7526D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="13_ncr:1_{110ACAF4-5F87-42D2-BA49-A95FA7526D7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{755E0BAA-3113-4BFD-A976-0293F67724B5}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="162913"/>
+  <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
     </ext>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
   </extLst>
 </workbook>
-</file>
-
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
@@ -79,6 +86,1691 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent1"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$A$1:$A$80</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="80"/>
+                <c:pt idx="0">
+                  <c:v>0</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.20799999999999999</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.41599999999999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.624</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.83199999999999996</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.04</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1.248</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.456</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>1.6639999999999999</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>1.8719999999999999</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2.08</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>2.2880000000000003</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2.4960000000000004</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>2.7040000000000006</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2.9120000000000008</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3.120000000000001</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>3.3280000000000012</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>3.5360000000000014</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3.7440000000000015</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>3.9520000000000017</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4.1600000000000019</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>4.3680000000000021</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>4.5760000000000023</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>4.7840000000000025</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>4.9920000000000027</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>5.2000000000000028</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>5.408000000000003</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>5.6160000000000032</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>5.8240000000000034</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>6.0320000000000036</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>6.2400000000000038</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>6.448000000000004</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>6.6560000000000041</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>6.8640000000000043</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>7.0720000000000045</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>7.2800000000000047</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>7.4880000000000049</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>7.6960000000000051</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>7.9040000000000052</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>8.1120000000000054</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>8.3200000000000056</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>8.5280000000000058</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>8.736000000000006</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>8.9440000000000062</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>9.1520000000000064</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>9.3600000000000065</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>9.5680000000000067</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>9.7760000000000069</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>9.9840000000000071</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>10.192000000000007</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>10.400000000000007</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>10.608000000000008</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>10.816000000000008</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>11.024000000000008</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>11.232000000000008</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>11.440000000000008</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>11.648000000000009</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>11.856000000000009</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>12.064000000000009</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>12.272000000000009</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>12.480000000000009</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>12.688000000000009</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>12.89600000000001</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>13.10400000000001</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>13.31200000000001</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>13.52000000000001</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>13.72800000000001</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>13.936000000000011</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>14.144000000000011</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>14.352000000000011</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>14.560000000000011</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>14.768000000000011</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>14.976000000000012</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>15.184000000000012</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>15.392000000000012</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>15.600000000000012</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>15.808000000000012</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>16.016000000000012</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>16.224000000000011</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>16.432000000000009</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-AC72-4E18-9C7E-7848CC0501F3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent2"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$B$1:$B$80</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="80"/>
+                <c:pt idx="0">
+                  <c:v>722</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>4042</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3032</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>3549</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3627</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>537</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>2944</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>4096</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>771</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>2290</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>4404</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>1186</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1655</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>4487</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>1748</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1113</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>4370</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>2387</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>717</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>4038</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3041</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>532</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>3544</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3637</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>541</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>2934</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>4101</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>776</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>2280</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>4409</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>1196</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1645</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>4487</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>1757</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1108</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>4365</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>2397</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>712</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>4033</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3100</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>522</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>3486</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3691</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>556</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>2871</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>4140</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>805</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>2216</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>4418</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>1240</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1591</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>4487</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>1811</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1059</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>4335</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>2460</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>688</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>3999</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>3110</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>517</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>3481</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>3696</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>561</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>2866</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>4145</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>810</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>2207</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>4423</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>1250</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1582</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>4487</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>1821</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1049</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>4335</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>2470</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>683</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>3989</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>3115</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>517</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-AC72-4E18-9C7E-7848CC0501F3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="circle"/>
+            <c:size val="5"/>
+            <c:spPr>
+              <a:solidFill>
+                <a:schemeClr val="accent3"/>
+              </a:solidFill>
+              <a:ln w="9525">
+                <a:solidFill>
+                  <a:schemeClr val="accent3"/>
+                </a:solidFill>
+              </a:ln>
+              <a:effectLst/>
+            </c:spPr>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>Sheet1!$C$1:$C$80</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="80"/>
+                <c:pt idx="0">
+                  <c:v>1694</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>2290</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>3476</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1923</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>3486</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>2221</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1738</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>3393</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>2548</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>1572</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>3198</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>2871</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>1503</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>2929</c:v>
+                </c:pt>
+                <c:pt idx="15">
+                  <c:v>3149</c:v>
+                </c:pt>
+                <c:pt idx="16">
+                  <c:v>1547</c:v>
+                </c:pt>
+                <c:pt idx="17">
+                  <c:v>2617</c:v>
+                </c:pt>
+                <c:pt idx="18">
+                  <c:v>3359</c:v>
+                </c:pt>
+                <c:pt idx="19">
+                  <c:v>1694</c:v>
+                </c:pt>
+                <c:pt idx="20">
+                  <c:v>2285</c:v>
+                </c:pt>
+                <c:pt idx="21">
+                  <c:v>3481</c:v>
+                </c:pt>
+                <c:pt idx="22">
+                  <c:v>1928</c:v>
+                </c:pt>
+                <c:pt idx="23">
+                  <c:v>1982</c:v>
+                </c:pt>
+                <c:pt idx="24">
+                  <c:v>3486</c:v>
+                </c:pt>
+                <c:pt idx="25">
+                  <c:v>2226</c:v>
+                </c:pt>
+                <c:pt idx="26">
+                  <c:v>1728</c:v>
+                </c:pt>
+                <c:pt idx="27">
+                  <c:v>3388</c:v>
+                </c:pt>
+                <c:pt idx="28">
+                  <c:v>2553</c:v>
+                </c:pt>
+                <c:pt idx="29">
+                  <c:v>1567</c:v>
+                </c:pt>
+                <c:pt idx="30">
+                  <c:v>3198</c:v>
+                </c:pt>
+                <c:pt idx="31">
+                  <c:v>2871</c:v>
+                </c:pt>
+                <c:pt idx="32">
+                  <c:v>1503</c:v>
+                </c:pt>
+                <c:pt idx="33">
+                  <c:v>2924</c:v>
+                </c:pt>
+                <c:pt idx="34">
+                  <c:v>3154</c:v>
+                </c:pt>
+                <c:pt idx="35">
+                  <c:v>1547</c:v>
+                </c:pt>
+                <c:pt idx="36">
+                  <c:v>2612</c:v>
+                </c:pt>
+                <c:pt idx="37">
+                  <c:v>3359</c:v>
+                </c:pt>
+                <c:pt idx="38">
+                  <c:v>1699</c:v>
+                </c:pt>
+                <c:pt idx="39">
+                  <c:v>2280</c:v>
+                </c:pt>
+                <c:pt idx="40">
+                  <c:v>3481</c:v>
+                </c:pt>
+                <c:pt idx="41">
+                  <c:v>1958</c:v>
+                </c:pt>
+                <c:pt idx="42">
+                  <c:v>1953</c:v>
+                </c:pt>
+                <c:pt idx="43">
+                  <c:v>3481</c:v>
+                </c:pt>
+                <c:pt idx="44">
+                  <c:v>2255</c:v>
+                </c:pt>
+                <c:pt idx="45">
+                  <c:v>1713</c:v>
+                </c:pt>
+                <c:pt idx="46">
+                  <c:v>3374</c:v>
+                </c:pt>
+                <c:pt idx="47">
+                  <c:v>2583</c:v>
+                </c:pt>
+                <c:pt idx="48">
+                  <c:v>1557</c:v>
+                </c:pt>
+                <c:pt idx="49">
+                  <c:v>3173</c:v>
+                </c:pt>
+                <c:pt idx="50">
+                  <c:v>2905</c:v>
+                </c:pt>
+                <c:pt idx="51">
+                  <c:v>1499</c:v>
+                </c:pt>
+                <c:pt idx="52">
+                  <c:v>2895</c:v>
+                </c:pt>
+                <c:pt idx="53">
+                  <c:v>3178</c:v>
+                </c:pt>
+                <c:pt idx="54">
+                  <c:v>1557</c:v>
+                </c:pt>
+                <c:pt idx="55">
+                  <c:v>2578</c:v>
+                </c:pt>
+                <c:pt idx="56">
+                  <c:v>3378</c:v>
+                </c:pt>
+                <c:pt idx="57">
+                  <c:v>1713</c:v>
+                </c:pt>
+                <c:pt idx="58">
+                  <c:v>2250</c:v>
+                </c:pt>
+                <c:pt idx="59">
+                  <c:v>3481</c:v>
+                </c:pt>
+                <c:pt idx="60">
+                  <c:v>1958</c:v>
+                </c:pt>
+                <c:pt idx="61">
+                  <c:v>1953</c:v>
+                </c:pt>
+                <c:pt idx="62">
+                  <c:v>3481</c:v>
+                </c:pt>
+                <c:pt idx="63">
+                  <c:v>2260</c:v>
+                </c:pt>
+                <c:pt idx="64">
+                  <c:v>1708</c:v>
+                </c:pt>
+                <c:pt idx="65">
+                  <c:v>3374</c:v>
+                </c:pt>
+                <c:pt idx="66">
+                  <c:v>2587</c:v>
+                </c:pt>
+                <c:pt idx="67">
+                  <c:v>1557</c:v>
+                </c:pt>
+                <c:pt idx="68">
+                  <c:v>3173</c:v>
+                </c:pt>
+                <c:pt idx="69">
+                  <c:v>2905</c:v>
+                </c:pt>
+                <c:pt idx="70">
+                  <c:v>1503</c:v>
+                </c:pt>
+                <c:pt idx="71">
+                  <c:v>2890</c:v>
+                </c:pt>
+                <c:pt idx="72">
+                  <c:v>3183</c:v>
+                </c:pt>
+                <c:pt idx="73">
+                  <c:v>1562</c:v>
+                </c:pt>
+                <c:pt idx="74">
+                  <c:v>2573</c:v>
+                </c:pt>
+                <c:pt idx="75">
+                  <c:v>3378</c:v>
+                </c:pt>
+                <c:pt idx="76">
+                  <c:v>1718</c:v>
+                </c:pt>
+                <c:pt idx="77">
+                  <c:v>2246</c:v>
+                </c:pt>
+                <c:pt idx="78">
+                  <c:v>3481</c:v>
+                </c:pt>
+                <c:pt idx="79">
+                  <c:v>1962</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-AC72-4E18-9C7E-7848CC0501F3}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="1612371984"/>
+        <c:axId val="1177027440"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="1612371984"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1177027440"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="1177027440"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1612371984"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="332">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>514350</xdr:colOff>
+      <xdr:row>5</xdr:row>
+      <xdr:rowOff>119062</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>14</xdr:col>
+      <xdr:colOff>209550</xdr:colOff>
+      <xdr:row>20</xdr:row>
+      <xdr:rowOff>4762</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{832216D8-F59A-6E61-88ED-0BADAAD2315D}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -344,650 +2036,976 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:B80"/>
+  <dimension ref="A1:C80"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="1">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
+      <c r="A1">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1">
         <v>722</v>
       </c>
-      <c r="B1">
+      <c r="C1">
         <v>1694</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2">
+        <f>A1+0.208</f>
+        <v>0.20799999999999999</v>
+      </c>
+      <c r="B2">
         <v>4042</v>
       </c>
-      <c r="B2">
+      <c r="C2">
         <v>2290</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3">
+        <f t="shared" ref="A3:A66" si="0">A2+0.208</f>
+        <v>0.41599999999999998</v>
+      </c>
+      <c r="B3">
         <v>3032</v>
       </c>
-      <c r="B3">
+      <c r="C3">
         <v>3476</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4">
+        <f t="shared" si="0"/>
+        <v>0.624</v>
+      </c>
+      <c r="B4">
         <v>532</v>
       </c>
-      <c r="B4">
+      <c r="C4">
         <v>1923</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5">
+        <f t="shared" si="0"/>
+        <v>0.83199999999999996</v>
+      </c>
+      <c r="B5">
         <v>3549</v>
       </c>
-      <c r="B5">
+      <c r="C5">
         <v>1982</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6">
+        <f t="shared" si="0"/>
+        <v>1.04</v>
+      </c>
+      <c r="B6">
         <v>3627</v>
       </c>
-      <c r="B6">
+      <c r="C6">
         <v>3486</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7">
+        <f t="shared" si="0"/>
+        <v>1.248</v>
+      </c>
+      <c r="B7">
         <v>537</v>
       </c>
-      <c r="B7">
+      <c r="C7">
         <v>2221</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8">
+        <f t="shared" si="0"/>
+        <v>1.456</v>
+      </c>
+      <c r="B8">
         <v>2944</v>
       </c>
-      <c r="B8">
+      <c r="C8">
         <v>1738</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9">
+        <f t="shared" si="0"/>
+        <v>1.6639999999999999</v>
+      </c>
+      <c r="B9">
         <v>4096</v>
       </c>
-      <c r="B9">
+      <c r="C9">
         <v>3393</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10">
+        <f t="shared" si="0"/>
+        <v>1.8719999999999999</v>
+      </c>
+      <c r="B10">
         <v>771</v>
       </c>
-      <c r="B10">
+      <c r="C10">
         <v>2548</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11">
+        <f t="shared" si="0"/>
+        <v>2.08</v>
+      </c>
+      <c r="B11">
         <v>2290</v>
       </c>
-      <c r="B11">
+      <c r="C11">
         <v>1572</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12">
+        <f t="shared" si="0"/>
+        <v>2.2880000000000003</v>
+      </c>
+      <c r="B12">
         <v>4404</v>
       </c>
-      <c r="B12">
+      <c r="C12">
         <v>3198</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13">
+        <f t="shared" si="0"/>
+        <v>2.4960000000000004</v>
+      </c>
+      <c r="B13">
         <v>1186</v>
       </c>
-      <c r="B13">
+      <c r="C13">
         <v>2871</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14">
+        <f t="shared" si="0"/>
+        <v>2.7040000000000006</v>
+      </c>
+      <c r="B14">
         <v>1655</v>
       </c>
-      <c r="B14">
+      <c r="C14">
         <v>1503</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15">
+        <f t="shared" si="0"/>
+        <v>2.9120000000000008</v>
+      </c>
+      <c r="B15">
         <v>4487</v>
       </c>
-      <c r="B15">
+      <c r="C15">
         <v>2929</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16">
+        <f t="shared" si="0"/>
+        <v>3.120000000000001</v>
+      </c>
+      <c r="B16">
         <v>1748</v>
       </c>
-      <c r="B16">
+      <c r="C16">
         <v>3149</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A17">
+        <f t="shared" si="0"/>
+        <v>3.3280000000000012</v>
+      </c>
+      <c r="B17">
         <v>1113</v>
       </c>
-      <c r="B17">
+      <c r="C17">
         <v>1547</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A18">
+        <f t="shared" si="0"/>
+        <v>3.5360000000000014</v>
+      </c>
+      <c r="B18">
         <v>4370</v>
       </c>
-      <c r="B18">
+      <c r="C18">
         <v>2617</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A19">
+        <f t="shared" si="0"/>
+        <v>3.7440000000000015</v>
+      </c>
+      <c r="B19">
         <v>2387</v>
       </c>
-      <c r="B19">
+      <c r="C19">
         <v>3359</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A20">
+        <f t="shared" si="0"/>
+        <v>3.9520000000000017</v>
+      </c>
+      <c r="B20">
         <v>717</v>
       </c>
-      <c r="B20">
+      <c r="C20">
         <v>1694</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A21">
+        <f t="shared" si="0"/>
+        <v>4.1600000000000019</v>
+      </c>
+      <c r="B21">
         <v>4038</v>
       </c>
-      <c r="B21">
+      <c r="C21">
         <v>2285</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A22">
+        <f t="shared" si="0"/>
+        <v>4.3680000000000021</v>
+      </c>
+      <c r="B22">
         <v>3041</v>
       </c>
-      <c r="B22">
+      <c r="C22">
         <v>3481</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A23">
+        <f t="shared" si="0"/>
+        <v>4.5760000000000023</v>
+      </c>
+      <c r="B23">
         <v>532</v>
       </c>
-      <c r="B23">
+      <c r="C23">
         <v>1928</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A24">
+        <f t="shared" si="0"/>
+        <v>4.7840000000000025</v>
+      </c>
+      <c r="B24">
         <v>3544</v>
       </c>
-      <c r="B24">
+      <c r="C24">
         <v>1982</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A25">
+        <f t="shared" si="0"/>
+        <v>4.9920000000000027</v>
+      </c>
+      <c r="B25">
         <v>3637</v>
       </c>
-      <c r="B25">
+      <c r="C25">
         <v>3486</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A26">
+        <f t="shared" si="0"/>
+        <v>5.2000000000000028</v>
+      </c>
+      <c r="B26">
         <v>541</v>
       </c>
-      <c r="B26">
+      <c r="C26">
         <v>2226</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A27">
+        <f t="shared" si="0"/>
+        <v>5.408000000000003</v>
+      </c>
+      <c r="B27">
         <v>2934</v>
       </c>
-      <c r="B27">
+      <c r="C27">
         <v>1728</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A28">
+        <f t="shared" si="0"/>
+        <v>5.6160000000000032</v>
+      </c>
+      <c r="B28">
         <v>4101</v>
       </c>
-      <c r="B28">
+      <c r="C28">
         <v>3388</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A29">
+        <f t="shared" si="0"/>
+        <v>5.8240000000000034</v>
+      </c>
+      <c r="B29">
         <v>776</v>
       </c>
-      <c r="B29">
+      <c r="C29">
         <v>2553</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A30">
+        <f t="shared" si="0"/>
+        <v>6.0320000000000036</v>
+      </c>
+      <c r="B30">
         <v>2280</v>
       </c>
-      <c r="B30">
+      <c r="C30">
         <v>1567</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A31">
+        <f t="shared" si="0"/>
+        <v>6.2400000000000038</v>
+      </c>
+      <c r="B31">
         <v>4409</v>
       </c>
-      <c r="B31">
+      <c r="C31">
         <v>3198</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A32">
+        <f t="shared" si="0"/>
+        <v>6.448000000000004</v>
+      </c>
+      <c r="B32">
         <v>1196</v>
       </c>
-      <c r="B32">
+      <c r="C32">
         <v>2871</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A33">
+        <f t="shared" si="0"/>
+        <v>6.6560000000000041</v>
+      </c>
+      <c r="B33">
         <v>1645</v>
       </c>
-      <c r="B33">
+      <c r="C33">
         <v>1503</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A34">
+        <f t="shared" si="0"/>
+        <v>6.8640000000000043</v>
+      </c>
+      <c r="B34">
         <v>4487</v>
       </c>
-      <c r="B34">
+      <c r="C34">
         <v>2924</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A35">
+        <f t="shared" si="0"/>
+        <v>7.0720000000000045</v>
+      </c>
+      <c r="B35">
         <v>1757</v>
       </c>
-      <c r="B35">
+      <c r="C35">
         <v>3154</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A36">
+        <f t="shared" si="0"/>
+        <v>7.2800000000000047</v>
+      </c>
+      <c r="B36">
         <v>1108</v>
       </c>
-      <c r="B36">
+      <c r="C36">
         <v>1547</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A37">
+        <f t="shared" si="0"/>
+        <v>7.4880000000000049</v>
+      </c>
+      <c r="B37">
         <v>4365</v>
       </c>
-      <c r="B37">
+      <c r="C37">
         <v>2612</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A38">
+        <f t="shared" si="0"/>
+        <v>7.6960000000000051</v>
+      </c>
+      <c r="B38">
         <v>2397</v>
       </c>
-      <c r="B38">
+      <c r="C38">
         <v>3359</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A39">
+        <f t="shared" si="0"/>
+        <v>7.9040000000000052</v>
+      </c>
+      <c r="B39">
         <v>712</v>
       </c>
-      <c r="B39">
+      <c r="C39">
         <v>1699</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A40">
+        <f t="shared" si="0"/>
+        <v>8.1120000000000054</v>
+      </c>
+      <c r="B40">
         <v>4033</v>
       </c>
-      <c r="B40">
+      <c r="C40">
         <v>2280</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A41">
+        <f t="shared" si="0"/>
+        <v>8.3200000000000056</v>
+      </c>
+      <c r="B41">
         <v>3100</v>
       </c>
-      <c r="B41">
+      <c r="C41">
         <v>3481</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A42">
+        <f t="shared" si="0"/>
+        <v>8.5280000000000058</v>
+      </c>
+      <c r="B42">
         <v>522</v>
       </c>
-      <c r="B42">
+      <c r="C42">
         <v>1958</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A43">
+        <f t="shared" si="0"/>
+        <v>8.736000000000006</v>
+      </c>
+      <c r="B43">
         <v>3486</v>
       </c>
-      <c r="B43">
+      <c r="C43">
         <v>1953</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A44">
+        <f t="shared" si="0"/>
+        <v>8.9440000000000062</v>
+      </c>
+      <c r="B44">
         <v>3691</v>
       </c>
-      <c r="B44">
+      <c r="C44">
         <v>3481</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A45">
+        <f t="shared" si="0"/>
+        <v>9.1520000000000064</v>
+      </c>
+      <c r="B45">
         <v>556</v>
       </c>
-      <c r="B45">
+      <c r="C45">
         <v>2255</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A46">
+        <f t="shared" si="0"/>
+        <v>9.3600000000000065</v>
+      </c>
+      <c r="B46">
         <v>2871</v>
       </c>
-      <c r="B46">
+      <c r="C46">
         <v>1713</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A47">
+        <f t="shared" si="0"/>
+        <v>9.5680000000000067</v>
+      </c>
+      <c r="B47">
         <v>4140</v>
       </c>
-      <c r="B47">
+      <c r="C47">
         <v>3374</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A48">
+        <f t="shared" si="0"/>
+        <v>9.7760000000000069</v>
+      </c>
+      <c r="B48">
         <v>805</v>
       </c>
-      <c r="B48">
+      <c r="C48">
         <v>2583</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A49">
+        <f t="shared" si="0"/>
+        <v>9.9840000000000071</v>
+      </c>
+      <c r="B49">
         <v>2216</v>
       </c>
-      <c r="B49">
+      <c r="C49">
         <v>1557</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A50">
+        <f t="shared" si="0"/>
+        <v>10.192000000000007</v>
+      </c>
+      <c r="B50">
         <v>4418</v>
       </c>
-      <c r="B50">
+      <c r="C50">
         <v>3173</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A51">
+        <f t="shared" si="0"/>
+        <v>10.400000000000007</v>
+      </c>
+      <c r="B51">
         <v>1240</v>
       </c>
-      <c r="B51">
+      <c r="C51">
         <v>2905</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A52">
+        <f t="shared" si="0"/>
+        <v>10.608000000000008</v>
+      </c>
+      <c r="B52">
         <v>1591</v>
       </c>
-      <c r="B52">
+      <c r="C52">
         <v>1499</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A53">
+        <f t="shared" si="0"/>
+        <v>10.816000000000008</v>
+      </c>
+      <c r="B53">
         <v>4487</v>
       </c>
-      <c r="B53">
+      <c r="C53">
         <v>2895</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A54">
+        <f t="shared" si="0"/>
+        <v>11.024000000000008</v>
+      </c>
+      <c r="B54">
         <v>1811</v>
       </c>
-      <c r="B54">
+      <c r="C54">
         <v>3178</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A55">
+        <f t="shared" si="0"/>
+        <v>11.232000000000008</v>
+      </c>
+      <c r="B55">
         <v>1059</v>
       </c>
-      <c r="B55">
+      <c r="C55">
         <v>1557</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A56">
+        <f t="shared" si="0"/>
+        <v>11.440000000000008</v>
+      </c>
+      <c r="B56">
         <v>4335</v>
       </c>
-      <c r="B56">
+      <c r="C56">
         <v>2578</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A57">
+        <f t="shared" si="0"/>
+        <v>11.648000000000009</v>
+      </c>
+      <c r="B57">
         <v>2460</v>
       </c>
-      <c r="B57">
+      <c r="C57">
         <v>3378</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A58">
+        <f t="shared" si="0"/>
+        <v>11.856000000000009</v>
+      </c>
+      <c r="B58">
         <v>688</v>
       </c>
-      <c r="B58">
+      <c r="C58">
         <v>1713</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A59">
+        <f t="shared" si="0"/>
+        <v>12.064000000000009</v>
+      </c>
+      <c r="B59">
         <v>3999</v>
       </c>
-      <c r="B59">
+      <c r="C59">
         <v>2250</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A60">
+        <f t="shared" si="0"/>
+        <v>12.272000000000009</v>
+      </c>
+      <c r="B60">
         <v>3110</v>
       </c>
-      <c r="B60">
+      <c r="C60">
         <v>3481</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A61">
+        <f t="shared" si="0"/>
+        <v>12.480000000000009</v>
+      </c>
+      <c r="B61">
         <v>517</v>
       </c>
-      <c r="B61">
+      <c r="C61">
         <v>1958</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A62">
+        <f t="shared" si="0"/>
+        <v>12.688000000000009</v>
+      </c>
+      <c r="B62">
         <v>3481</v>
       </c>
-      <c r="B62">
+      <c r="C62">
         <v>1953</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A63">
+        <f t="shared" si="0"/>
+        <v>12.89600000000001</v>
+      </c>
+      <c r="B63">
         <v>3696</v>
       </c>
-      <c r="B63">
+      <c r="C63">
         <v>3481</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A64">
+        <f t="shared" si="0"/>
+        <v>13.10400000000001</v>
+      </c>
+      <c r="B64">
         <v>561</v>
       </c>
-      <c r="B64">
+      <c r="C64">
         <v>2260</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A65">
+        <f t="shared" si="0"/>
+        <v>13.31200000000001</v>
+      </c>
+      <c r="B65">
         <v>2866</v>
       </c>
-      <c r="B65">
+      <c r="C65">
         <v>1708</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A66">
+        <f t="shared" si="0"/>
+        <v>13.52000000000001</v>
+      </c>
+      <c r="B66">
         <v>4145</v>
       </c>
-      <c r="B66">
+      <c r="C66">
         <v>3374</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A67">
+        <f t="shared" ref="A67:A80" si="1">A66+0.208</f>
+        <v>13.72800000000001</v>
+      </c>
+      <c r="B67">
         <v>810</v>
       </c>
-      <c r="B67">
+      <c r="C67">
         <v>2587</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A68">
+        <f t="shared" si="1"/>
+        <v>13.936000000000011</v>
+      </c>
+      <c r="B68">
         <v>2207</v>
       </c>
-      <c r="B68">
+      <c r="C68">
         <v>1557</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A69">
+        <f t="shared" si="1"/>
+        <v>14.144000000000011</v>
+      </c>
+      <c r="B69">
         <v>4423</v>
       </c>
-      <c r="B69">
+      <c r="C69">
         <v>3173</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A70">
+        <f t="shared" si="1"/>
+        <v>14.352000000000011</v>
+      </c>
+      <c r="B70">
         <v>1250</v>
       </c>
-      <c r="B70">
+      <c r="C70">
         <v>2905</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A71">
+        <f t="shared" si="1"/>
+        <v>14.560000000000011</v>
+      </c>
+      <c r="B71">
         <v>1582</v>
       </c>
-      <c r="B71">
+      <c r="C71">
         <v>1503</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A72">
+        <f t="shared" si="1"/>
+        <v>14.768000000000011</v>
+      </c>
+      <c r="B72">
         <v>4487</v>
       </c>
-      <c r="B72">
+      <c r="C72">
         <v>2890</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A73">
+        <f t="shared" si="1"/>
+        <v>14.976000000000012</v>
+      </c>
+      <c r="B73">
         <v>1821</v>
       </c>
-      <c r="B73">
+      <c r="C73">
         <v>3183</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A74">
+        <f t="shared" si="1"/>
+        <v>15.184000000000012</v>
+      </c>
+      <c r="B74">
         <v>1049</v>
       </c>
-      <c r="B74">
+      <c r="C74">
         <v>1562</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A75">
+        <f t="shared" si="1"/>
+        <v>15.392000000000012</v>
+      </c>
+      <c r="B75">
         <v>4335</v>
       </c>
-      <c r="B75">
+      <c r="C75">
         <v>2573</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A76">
+        <f t="shared" si="1"/>
+        <v>15.600000000000012</v>
+      </c>
+      <c r="B76">
         <v>2470</v>
       </c>
-      <c r="B76">
+      <c r="C76">
         <v>3378</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A77">
+        <f t="shared" si="1"/>
+        <v>15.808000000000012</v>
+      </c>
+      <c r="B77">
         <v>683</v>
       </c>
-      <c r="B77">
+      <c r="C77">
         <v>1718</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A78">
+        <f t="shared" si="1"/>
+        <v>16.016000000000012</v>
+      </c>
+      <c r="B78">
         <v>3989</v>
       </c>
-      <c r="B78">
+      <c r="C78">
         <v>2246</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A79">
+        <f t="shared" si="1"/>
+        <v>16.224000000000011</v>
+      </c>
+      <c r="B79">
         <v>3115</v>
       </c>
-      <c r="B79">
+      <c r="C79">
         <v>3481</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A80">
+        <f t="shared" si="1"/>
+        <v>16.432000000000009</v>
+      </c>
+      <c r="B80">
         <v>517</v>
       </c>
-      <c r="B80">
+      <c r="C80">
         <v>1962</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <drawing r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{d1b36e95-0d50-42e9-958f-b63fa906beaa}" enabled="0" method="" siteId="{d1b36e95-0d50-42e9-958f-b63fa906beaa}" removed="1"/>
+</clbl:labelList>
 </file>